--- a/data_xlsx_archive/志明AI實驗數據_6_1-6_30.xlsx
+++ b/data_xlsx_archive/志明AI實驗數據_6_1-6_30.xlsx
@@ -124,10 +124,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -159,10 +159,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2674,7 +2674,7 @@
         <v>期間</v>
       </c>
       <c r="B6" t="str">
-        <v>2026/6/1 – 6/25</v>
+        <v>2026/6/1 – 6/30</v>
       </c>
     </row>
     <row r="7">
@@ -2682,7 +2682,7 @@
         <v>總組數</v>
       </c>
       <c r="B7" t="str">
-        <v>37 組（跨型態 29、文案 7、其他 1）</v>
+        <v>50 組（跨型態 42、文案 7、其他 1）</v>
       </c>
     </row>
     <row r="8">
